--- a/EstablecimientoSalud/excels/CALLAO-CALLAO-CALLAO.xlsx
+++ b/EstablecimientoSalud/excels/CALLAO-CALLAO-CALLAO.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L67"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>6251</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>70104</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-12.06920504</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>6233</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-12.0265051</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>6239</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-12.00969499</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>29132</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>70103</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CARMEN DE LA LEGUA REYNOSO</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-12.04012691</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>6253</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>70103</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>CARMEN DE LA LEGUA REYNOSO</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-12.04196315</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>7314</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>70106</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-11.83265968</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>10261</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>70106</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-11.88545383</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>6262</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>70106</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-11.88563281</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>29380</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>70106</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-11.87726528</t>
@@ -1040,40 +995,35 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>6243</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-11.99616332</t>
@@ -1102,40 +1052,35 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>6256</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>70106</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-11.82855773</t>
@@ -1164,40 +1109,35 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>6235</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-12.04578311</t>
@@ -1226,40 +1166,35 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>7948</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-12.0150475</t>
@@ -1288,40 +1223,35 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>6244</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-11.99509597</t>
@@ -1350,40 +1280,35 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>6248</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-12.02515855</t>
@@ -1412,40 +1337,35 @@
       <c r="K16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>26983</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>70104</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-12.06951082</t>
@@ -1474,40 +1394,35 @@
       <c r="K17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>10255</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>70105</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>LA PUNTA</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-12.07136543</t>
@@ -1536,40 +1451,35 @@
       <c r="K18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>6224</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-12.05330245</t>
@@ -1598,40 +1508,35 @@
       <c r="K19" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>6226</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-12.04658449</t>
@@ -1660,40 +1565,35 @@
       <c r="K20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>8146</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>70106</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-11.8865243</t>
@@ -1722,40 +1622,35 @@
       <c r="K21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>6268</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>70106</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-11.87633106</t>
@@ -1784,40 +1679,35 @@
       <c r="K22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>6267</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>70106</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-11.84677854</t>
@@ -1846,40 +1736,35 @@
       <c r="K23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>6225</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-12.04850915</t>
@@ -1908,40 +1793,35 @@
       <c r="K24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>6250</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>70104</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-12.06951429</t>
@@ -1970,40 +1850,35 @@
       <c r="K25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>6258</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>70106</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-11.93696178</t>
@@ -2032,40 +1907,35 @@
       <c r="K26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>6221</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-12.05394219</t>
@@ -2094,40 +1964,35 @@
       <c r="K27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>6246</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-12.00186975</t>
@@ -2156,40 +2021,35 @@
       <c r="K28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>6227</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>70105</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>LA PUNTA</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-12.06837287</t>
@@ -2218,40 +2078,35 @@
       <c r="K29" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>6230</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-12.02215478</t>
@@ -2280,40 +2135,35 @@
       <c r="K30" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>6234</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>-12.04586988</t>
@@ -2342,40 +2192,35 @@
       <c r="K31" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>6242</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-12.03794156</t>
@@ -2404,40 +2249,35 @@
       <c r="K32" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>6255</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>70106</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>-11.87255066</t>
@@ -2466,40 +2306,35 @@
       <c r="K33" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>6259</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>70106</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>-11.94239104</t>
@@ -2528,40 +2363,35 @@
       <c r="K34" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>6261</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>70106</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>-11.82445218</t>
@@ -2590,40 +2420,35 @@
       <c r="K35" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>6263</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>70106</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>-11.84707868</t>
@@ -2652,40 +2477,35 @@
       <c r="K36" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>6220</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>-12.06225097</t>
@@ -2714,40 +2534,35 @@
       <c r="K37" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>6266</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>70106</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>-11.82924006</t>
@@ -2776,40 +2591,35 @@
       <c r="K38" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>6231</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>-12.0410186</t>
@@ -2838,40 +2648,35 @@
       <c r="K39" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>6264</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>70106</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>-11.83522846</t>
@@ -2900,40 +2705,35 @@
       <c r="K40" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>10451</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>-12.01221274</t>
@@ -2962,40 +2762,35 @@
       <c r="K41" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>10573</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>70106</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>-11.87151</t>
@@ -3024,40 +2819,35 @@
       <c r="K42" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>24761</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>-12.0508491</t>
@@ -3086,40 +2876,35 @@
       <c r="K43" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>6222</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>-12.05194895</t>
@@ -3148,40 +2933,35 @@
       <c r="K44" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>31271</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>70102</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>-12.0613052</t>
@@ -3210,40 +2990,35 @@
       <c r="K45" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>10258</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>-12.03501833</t>
@@ -3272,40 +3047,35 @@
       <c r="K46" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>6768</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>-11.97311497</t>
@@ -3334,40 +3104,35 @@
       <c r="K47" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>6260</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>70107</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>MI PERU</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>-11.85554679</t>
@@ -3396,40 +3161,35 @@
       <c r="K48" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>10557</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>70104</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>LA PERLA</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>-12.0723635</t>
@@ -3458,40 +3218,35 @@
       <c r="K49" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>30821</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>70102</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>-12.0638138</t>
@@ -3520,40 +3275,35 @@
       <c r="K50" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>36133</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>-12.0670007</t>
@@ -3582,40 +3332,35 @@
       <c r="K51" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>6249</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>70102</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>BELLAVISTA</t>
-        </is>
-      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>-12.06171682</t>
@@ -3644,40 +3389,35 @@
       <c r="K52" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>20823</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>-12.02307765</t>
@@ -3706,40 +3446,35 @@
       <c r="K53" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>6252</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>70103</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>CARMEN DE LA LEGUA REYNOSO</t>
-        </is>
-      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>-12.04001323</t>
@@ -3768,40 +3503,35 @@
       <c r="K54" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>6241</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>-12.03365706</t>
@@ -3830,40 +3560,35 @@
       <c r="K55" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>6245</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F56" t="inlineStr">
         <is>
           <t>-12.02421866</t>
@@ -3892,40 +3617,35 @@
       <c r="K56" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>6223</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>-12.05410129</t>
@@ -3954,40 +3674,35 @@
       <c r="K57" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
           <t>6238</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F58" t="inlineStr">
         <is>
           <t>-11.94257438</t>
@@ -4016,40 +3731,35 @@
       <c r="K58" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
           <t>6240</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F59" t="inlineStr">
         <is>
           <t>-12.01652914</t>
@@ -4078,40 +3788,35 @@
       <c r="K59" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
           <t>6228</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F60" t="inlineStr">
         <is>
           <t>-12.04253586</t>
@@ -4140,40 +3845,35 @@
       <c r="K60" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
           <t>6257</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>70106</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>VENTANILLA</t>
-        </is>
-      </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>-11.89274295</t>
@@ -4202,40 +3902,35 @@
       <c r="K61" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
           <t>10660</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>-12.03551396</t>
@@ -4264,40 +3959,35 @@
       <c r="K62" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
           <t>6668</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F63" t="inlineStr">
         <is>
           <t>-12.06067896</t>
@@ -4326,40 +4016,35 @@
       <c r="K63" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
           <t>10260</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F64" t="inlineStr">
         <is>
           <t>-12.0318924</t>
@@ -4388,40 +4073,35 @@
       <c r="K64" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
           <t>10257</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F65" t="inlineStr">
         <is>
           <t>-12.0345625</t>
@@ -4450,40 +4130,35 @@
       <c r="K65" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
           <t>18327</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F66" t="inlineStr">
         <is>
           <t>-12.02207209</t>
@@ -4512,40 +4187,35 @@
       <c r="K66" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>070101</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CALLAO</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
           <t>33842</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>70101</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>CALLAO</t>
-        </is>
-      </c>
       <c r="F67" t="inlineStr">
         <is>
           <t>-12.0438386</t>
@@ -4574,11 +4244,6 @@
       <c r="K67" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>070101</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/CALLAO-CALLAO-CALLAO.xlsx
+++ b/EstablecimientoSalud/excels/CALLAO-CALLAO-CALLAO.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
